--- a/drg/menaka dd/archi/calculations load/wall load calculation.xlsx
+++ b/drg/menaka dd/archi/calculations load/wall load calculation.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933A39FF-BCB5-43D5-99B6-DCBA8E45228F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79D762C-B6B5-4FCB-89B1-23B397B93E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5985" yWindow="1095" windowWidth="13050" windowHeight="10050" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interpoaltion" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="61">
   <si>
     <t>y-y1=((y2-y1)/(x2-x1))*(x-x1)</t>
   </si>
@@ -933,7 +933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF5F103-52A0-4D11-811D-43BFE2FAABA8}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -946,9 +946,16 @@
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>3</v>
       </c>
@@ -972,8 +979,31 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="31"/>
+      <c r="S1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+    </row>
+    <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30"/>
       <c r="B2" s="30"/>
       <c r="C2" s="3" t="s">
@@ -997,8 +1027,31 @@
         <v>30</v>
       </c>
       <c r="K2" s="34"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="34"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="34"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="3"/>
@@ -1018,8 +1071,27 @@
       <c r="K3" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="U3" s="16"/>
+      <c r="V3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1057,8 +1129,45 @@
         <f>0.75*H4</f>
         <v>9.0258900000000022</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="2">
+        <v>20</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>Q15</f>
+        <v>2.3113999999999999</v>
+      </c>
+      <c r="R4" s="14">
+        <f>Q16</f>
+        <v>2.6162000000000001</v>
+      </c>
+      <c r="S4" s="12">
+        <f>P4*Q4*O4</f>
+        <v>10.632440000000001</v>
+      </c>
+      <c r="T4" s="13">
+        <f>P4*R4*O4</f>
+        <v>12.034520000000002</v>
+      </c>
+      <c r="U4" s="17"/>
+      <c r="V4" s="12">
+        <f>0.75*S4</f>
+        <v>7.9743300000000001</v>
+      </c>
+      <c r="W4" s="13">
+        <f>0.75*T4</f>
+        <v>9.0258900000000022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -1092,8 +1201,41 @@
         <f>0.75*H5</f>
         <v>9.0258900000000022</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2">
+        <f>Q17</f>
+        <v>2.3113999999999999</v>
+      </c>
+      <c r="R5" s="14">
+        <f>Q18</f>
+        <v>2.6162000000000001</v>
+      </c>
+      <c r="S5" s="12">
+        <f>P4*Q5*O4</f>
+        <v>10.632440000000001</v>
+      </c>
+      <c r="T5" s="13">
+        <f>P4*R5*O4</f>
+        <v>12.034520000000002</v>
+      </c>
+      <c r="U5" s="17"/>
+      <c r="V5" s="12">
+        <f>0.75*S5</f>
+        <v>7.9743300000000001</v>
+      </c>
+      <c r="W5" s="13">
+        <f>0.75*T5</f>
+        <v>9.0258900000000022</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
@@ -1105,8 +1247,19 @@
       <c r="I6" s="17"/>
       <c r="J6" s="12"/>
       <c r="K6" s="13"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M6" s="3"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="13"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1144,8 +1297,45 @@
         <f>0.75*H7</f>
         <v>4.5129450000000011</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="2">
+        <v>20</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.115</v>
+      </c>
+      <c r="Q7" s="2">
+        <f>Q4</f>
+        <v>2.3113999999999999</v>
+      </c>
+      <c r="R7" s="14">
+        <f>R4</f>
+        <v>2.6162000000000001</v>
+      </c>
+      <c r="S7" s="12">
+        <f>P7*Q7*O7</f>
+        <v>5.3162200000000004</v>
+      </c>
+      <c r="T7" s="13">
+        <f>P7*R7*O7</f>
+        <v>6.0172600000000012</v>
+      </c>
+      <c r="U7" s="17"/>
+      <c r="V7" s="12">
+        <f>0.75*S7</f>
+        <v>3.9871650000000001</v>
+      </c>
+      <c r="W7" s="13">
+        <f>0.75*T7</f>
+        <v>4.5129450000000011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -1179,8 +1369,41 @@
         <f>0.75*H8</f>
         <v>4.5129450000000011</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2">
+        <f>Q5</f>
+        <v>2.3113999999999999</v>
+      </c>
+      <c r="R8" s="14">
+        <f>R5</f>
+        <v>2.6162000000000001</v>
+      </c>
+      <c r="S8" s="12">
+        <f>P7*Q8*O7</f>
+        <v>5.3162200000000004</v>
+      </c>
+      <c r="T8" s="13">
+        <f>P7*R8*O7</f>
+        <v>6.0172600000000012</v>
+      </c>
+      <c r="U8" s="17"/>
+      <c r="V8" s="12">
+        <f>0.75*S8</f>
+        <v>3.9871650000000001</v>
+      </c>
+      <c r="W8" s="13">
+        <f>0.75*T8</f>
+        <v>4.5129450000000011</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
@@ -1192,8 +1415,19 @@
       <c r="I9" s="20"/>
       <c r="J9" s="18"/>
       <c r="K9" s="19"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="3"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="19"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1219,8 +1453,33 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
       <c r="K10" s="37"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="2">
+        <v>20</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.115</v>
+      </c>
+      <c r="Q10" s="28">
+        <f>Q19</f>
+        <v>0.91439999999999999</v>
+      </c>
+      <c r="R10" s="29"/>
+      <c r="S10" s="35">
+        <f>P10*Q10*O10</f>
+        <v>2.1031200000000001</v>
+      </c>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="37"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1231,8 +1490,18 @@
       <c r="E14" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14" s="8"/>
+      <c r="P14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1244,8 +1513,19 @@
         <f>CONVERT(D15,"in","m")</f>
         <v>2.3875999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="1">
+        <f>7*12+7</f>
+        <v>91</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>CONVERT(P15,"in","m")</f>
+        <v>2.3113999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D16" s="1">
         <f>8*12+7</f>
         <v>103</v>
@@ -1254,8 +1534,16 @@
         <f>CONVERT(D16,"in","m")</f>
         <v>2.6162000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="P16" s="1">
+        <f>8*12+7</f>
+        <v>103</v>
+      </c>
+      <c r="Q16" s="2">
+        <f>CONVERT(P16,"in","m")</f>
+        <v>2.6162000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D17" s="1">
         <f>7*12+10</f>
         <v>94</v>
@@ -1264,8 +1552,16 @@
         <f>CONVERT(D17,"in","m")</f>
         <v>2.3875999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="P17" s="1">
+        <f>7*12+7</f>
+        <v>91</v>
+      </c>
+      <c r="Q17" s="2">
+        <f>CONVERT(P17,"in","m")</f>
+        <v>2.3113999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <f>8*12+7</f>
         <v>103</v>
@@ -1274,8 +1570,16 @@
         <f>CONVERT(D18,"in","m")</f>
         <v>2.6162000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="P18" s="1">
+        <f>8*12+7</f>
+        <v>103</v>
+      </c>
+      <c r="Q18" s="2">
+        <f>CONVERT(P18,"in","m")</f>
+        <v>2.6162000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D19" s="1">
         <f>3*12</f>
         <v>36</v>
@@ -1284,9 +1588,25 @@
         <f>CONVERT(D19,"in","m")</f>
         <v>0.91439999999999999</v>
       </c>
+      <c r="P19" s="1">
+        <f>3*12</f>
+        <v>36</v>
+      </c>
+      <c r="Q19" s="2">
+        <f>CONVERT(P19,"in","m")</f>
+        <v>0.91439999999999999</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="16">
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:W1"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="V2:W2"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="E1:F1"/>

--- a/drg/menaka dd/archi/calculations load/wall load calculation.xlsx
+++ b/drg/menaka dd/archi/calculations load/wall load calculation.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79D762C-B6B5-4FCB-89B1-23B397B93E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3242CF06-6161-471A-AA69-322D5D869DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5985" yWindow="1095" windowWidth="13050" windowHeight="10050" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="480" windowWidth="13104" windowHeight="11256" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interpoaltion" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="94">
   <si>
     <t>y-y1=((y2-y1)/(x2-x1))*(x-x1)</t>
   </si>
@@ -215,13 +215,302 @@
   </si>
   <si>
     <t>8mm C/C (at top and bottom) @100mm&amp; @ 150 8mm C/C (at mid height) in all columns</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>5A</t>
+  </si>
+  <si>
+    <t>6A</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>Type of beam</t>
+  </si>
+  <si>
+    <t>Size of beam</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>Bottom</t>
+  </si>
+  <si>
+    <t>Reinforcement detail at support</t>
+  </si>
+  <si>
+    <t>Reinforcement detail at center</t>
+  </si>
+  <si>
+    <t>Tie beam</t>
+  </si>
+  <si>
+    <t>X-dir</t>
+  </si>
+  <si>
+    <t>Y-dir</t>
+  </si>
+  <si>
+    <r>
+      <t>3-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th+1-16mmφ Ex</t>
+    </r>
+  </si>
+  <si>
+    <t>First &amp; second floor Main beam</t>
+  </si>
+  <si>
+    <t>Ground floor secondary beam</t>
+  </si>
+  <si>
+    <t>Ground floor main beam</t>
+  </si>
+  <si>
+    <t>304.8*431.8</t>
+  </si>
+  <si>
+    <r>
+      <t>2-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th +1-16mmφ Ex</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th +2-12mmφ Ex</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th +2-16mmφ Ex</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th +1-12mmφ Ex</t>
+    </r>
+  </si>
+  <si>
+    <t>Third &amp; fourth floor Main beam</t>
+  </si>
+  <si>
+    <t>230*355.6</t>
+  </si>
+  <si>
+    <r>
+      <t>3-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th +</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2-16mmφ Ex</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-16mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>φ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Th +1-16mmφ Ex +1-12mmφ Ex</t>
+    </r>
+  </si>
+  <si>
+    <t>Roof floor Main beam</t>
+  </si>
+  <si>
+    <t>First &amp; second floor Secondary beam</t>
+  </si>
+  <si>
+    <t>Third &amp; fourth floor Secondary beam</t>
+  </si>
+  <si>
+    <t>Roof floor Secondary beam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,8 +538,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,6 +561,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -519,18 +826,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -549,7 +849,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -574,6 +873,15 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -589,15 +897,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -605,6 +904,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -888,9 +1227,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -898,7 +1237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>0.5</v>
       </c>
@@ -906,7 +1245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>0.71799999999999997</v>
       </c>
@@ -918,7 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2.5</v>
       </c>
@@ -934,32 +1273,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF5F103-52A0-4D11-811D-43BFE2FAABA8}">
   <dimension ref="A1:W19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
     <col min="7" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -968,21 +1307,21 @@
       <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="M1" s="30" t="s">
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="M1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="29" t="s">
         <v>26</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -991,21 +1330,21 @@
       <c r="P1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="31" t="s">
+      <c r="Q1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="31"/>
-      <c r="S1" s="32" t="s">
+      <c r="R1" s="30"/>
+      <c r="S1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-    </row>
-    <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+    </row>
+    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
       <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
@@ -1015,20 +1354,20 @@
       <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="33" t="s">
+      <c r="H2" s="33"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="34"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
+      <c r="K2" s="33"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
       <c r="O2" s="3" t="s">
         <v>16</v>
       </c>
@@ -1038,60 +1377,60 @@
       <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="33" t="s">
+      <c r="T2" s="33"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="W2" s="34"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="W2" s="33"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="10" t="s">
+      <c r="I3" s="13"/>
+      <c r="J3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="10" t="s">
+      <c r="R3" s="6"/>
+      <c r="S3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="16"/>
-      <c r="V3" s="10" t="s">
+      <c r="U3" s="13"/>
+      <c r="V3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="W3" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1108,24 +1447,24 @@
         <f>E15</f>
         <v>2.3875999999999999</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <f>E16</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="9">
         <f>D4*E4*C4</f>
         <v>10.982959999999999</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="10">
         <f>D4*F4*C4</f>
         <v>12.034520000000002</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="12">
+      <c r="I4" s="14"/>
+      <c r="J4" s="9">
         <f>0.75*G4</f>
         <v>8.2372199999999989</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="10">
         <f>0.75*H4</f>
         <v>9.0258900000000022</v>
       </c>
@@ -1145,29 +1484,29 @@
         <f>Q15</f>
         <v>2.3113999999999999</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="11">
         <f>Q16</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="S4" s="12">
+      <c r="S4" s="9">
         <f>P4*Q4*O4</f>
         <v>10.632440000000001</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="10">
         <f>P4*R4*O4</f>
         <v>12.034520000000002</v>
       </c>
-      <c r="U4" s="17"/>
-      <c r="V4" s="12">
+      <c r="U4" s="14"/>
+      <c r="V4" s="9">
         <f>0.75*S4</f>
         <v>7.9743300000000001</v>
       </c>
-      <c r="W4" s="13">
+      <c r="W4" s="10">
         <f>0.75*T4</f>
         <v>9.0258900000000022</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -1180,24 +1519,24 @@
         <f>E17</f>
         <v>2.3875999999999999</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="11">
         <f>E18</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="9">
         <f>D4*E5*C4</f>
         <v>10.982959999999999</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="10">
         <f>D4*F5*C4</f>
         <v>12.034520000000002</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="12">
+      <c r="I5" s="14"/>
+      <c r="J5" s="9">
         <f>0.75*G5</f>
         <v>8.2372199999999989</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="10">
         <f>0.75*H5</f>
         <v>9.0258900000000022</v>
       </c>
@@ -1213,53 +1552,53 @@
         <f>Q17</f>
         <v>2.3113999999999999</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="11">
         <f>Q18</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="9">
         <f>P4*Q5*O4</f>
         <v>10.632440000000001</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="10">
         <f>P4*R5*O4</f>
         <v>12.034520000000002</v>
       </c>
-      <c r="U5" s="17"/>
-      <c r="V5" s="12">
+      <c r="U5" s="14"/>
+      <c r="V5" s="9">
         <f>0.75*S5</f>
         <v>7.9743300000000001</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="10">
         <f>0.75*T5</f>
         <v>9.0258900000000022</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="13"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="10"/>
       <c r="M6" s="3"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="13"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R6" s="11"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="10"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1276,24 +1615,24 @@
         <f>E4</f>
         <v>2.3875999999999999</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="11">
         <f>F4</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="9">
         <f>D7*E7*C7</f>
         <v>5.4914799999999993</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="10">
         <f>D7*F7*C7</f>
         <v>6.0172600000000012</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="12">
+      <c r="I7" s="14"/>
+      <c r="J7" s="9">
         <f>0.75*G7</f>
         <v>4.1186099999999994</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="10">
         <f>0.75*H7</f>
         <v>4.5129450000000011</v>
       </c>
@@ -1313,29 +1652,29 @@
         <f>Q4</f>
         <v>2.3113999999999999</v>
       </c>
-      <c r="R7" s="14">
+      <c r="R7" s="11">
         <f>R4</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="9">
         <f>P7*Q7*O7</f>
         <v>5.3162200000000004</v>
       </c>
-      <c r="T7" s="13">
+      <c r="T7" s="10">
         <f>P7*R7*O7</f>
         <v>6.0172600000000012</v>
       </c>
-      <c r="U7" s="17"/>
-      <c r="V7" s="12">
+      <c r="U7" s="14"/>
+      <c r="V7" s="9">
         <f>0.75*S7</f>
         <v>3.9871650000000001</v>
       </c>
-      <c r="W7" s="13">
+      <c r="W7" s="10">
         <f>0.75*T7</f>
         <v>4.5129450000000011</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -1348,24 +1687,24 @@
         <f>E5</f>
         <v>2.3875999999999999</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <f>F5</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="9">
         <f>D7*E8*C7</f>
         <v>5.4914799999999993</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <f>D7*F8*C7</f>
         <v>6.0172600000000012</v>
       </c>
-      <c r="I8" s="17"/>
-      <c r="J8" s="12">
+      <c r="I8" s="14"/>
+      <c r="J8" s="9">
         <f>0.75*G8</f>
         <v>4.1186099999999994</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="10">
         <f>0.75*H8</f>
         <v>4.5129450000000011</v>
       </c>
@@ -1381,53 +1720,53 @@
         <f>Q5</f>
         <v>2.3113999999999999</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="11">
         <f>R5</f>
         <v>2.6162000000000001</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="9">
         <f>P7*Q8*O7</f>
         <v>5.3162200000000004</v>
       </c>
-      <c r="T8" s="13">
+      <c r="T8" s="10">
         <f>P7*R8*O7</f>
         <v>6.0172600000000012</v>
       </c>
-      <c r="U8" s="17"/>
-      <c r="V8" s="12">
+      <c r="U8" s="14"/>
+      <c r="V8" s="9">
         <f>0.75*S8</f>
         <v>3.9871650000000001</v>
       </c>
-      <c r="W8" s="13">
+      <c r="W8" s="10">
         <f>0.75*T8</f>
         <v>4.5129450000000011</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="16"/>
       <c r="M9" s="3"/>
       <c r="N9" s="1"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="19"/>
-    </row>
-    <row r="10" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R9" s="11"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="16"/>
+    </row>
+    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1440,19 +1779,19 @@
       <c r="D10" s="2">
         <v>0.115</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="24">
         <f>E19</f>
         <v>0.91439999999999999</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="35">
+      <c r="F10" s="25"/>
+      <c r="G10" s="26">
         <f>D10*E10*C10</f>
         <v>2.1031200000000001</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="37"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="28"/>
       <c r="M10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1465,25 +1804,25 @@
       <c r="P10" s="2">
         <v>0.115</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="24">
         <f>Q19</f>
         <v>0.91439999999999999</v>
       </c>
-      <c r="R10" s="29"/>
-      <c r="S10" s="35">
+      <c r="R10" s="25"/>
+      <c r="S10" s="26">
         <f>P10*Q10*O10</f>
         <v>2.1031200000000001</v>
       </c>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="37"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="28"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="5"/>
       <c r="D14" s="3" t="s">
         <v>17</v>
       </c>
@@ -1493,7 +1832,7 @@
       <c r="M14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="8"/>
+      <c r="N14" s="5"/>
       <c r="P14" s="3" t="s">
         <v>17</v>
       </c>
@@ -1501,7 +1840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1525,7 +1864,7 @@
         <v>2.3113999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D16" s="1">
         <f>8*12+7</f>
         <v>103</v>
@@ -1543,7 +1882,7 @@
         <v>2.6162000000000001</v>
       </c>
     </row>
-    <row r="17" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D17" s="1">
         <f>7*12+10</f>
         <v>94</v>
@@ -1561,7 +1900,7 @@
         <v>2.3113999999999999</v>
       </c>
     </row>
-    <row r="18" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D18" s="1">
         <f>8*12+7</f>
         <v>103</v>
@@ -1579,7 +1918,7 @@
         <v>2.6162000000000001</v>
       </c>
     </row>
-    <row r="19" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D19" s="1">
         <f>3*12</f>
         <v>36</v>
@@ -1599,6 +1938,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="G10:K10"/>
     <mergeCell ref="Q10:R10"/>
     <mergeCell ref="S10:W10"/>
     <mergeCell ref="M1:M2"/>
@@ -1607,14 +1954,6 @@
     <mergeCell ref="S1:W1"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="V2:W2"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="G10:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1622,273 +1961,813 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C53DFB-C26A-4789-93E0-5F02EDBF3A4E}">
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" style="41" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="41" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="41" customWidth="1"/>
+    <col min="7" max="10" width="12.88671875" style="41" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="41" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:17" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="37"/>
+      <c r="E1" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="H1" s="37"/>
+      <c r="I1" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="L1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="M1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="N1" s="37" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45">
         <v>8</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="46">
         <f>(A2*A2*PI())/4</f>
         <v>50.26548245743669</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="46">
         <f>2*B2</f>
         <v>100.53096491487338</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46">
+        <f>3*B2</f>
+        <v>150.79644737231007</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46">
         <f>4*B2</f>
         <v>201.06192982974676</v>
       </c>
-      <c r="E2" s="2">
+      <c r="H2" s="46"/>
+      <c r="I2" s="46">
+        <f>5*B2</f>
+        <v>251.32741228718345</v>
+      </c>
+      <c r="J2" s="46">
+        <f>6*B2</f>
+        <v>301.59289474462014</v>
+      </c>
+      <c r="K2" s="46">
         <f>8*B2</f>
         <v>402.12385965949352</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="L2" s="39"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+    </row>
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="45">
         <v>10</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="46">
         <f t="shared" ref="B4:B12" si="0">(A4*A4*PI())/4</f>
         <v>78.539816339744831</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="46">
         <f t="shared" ref="C4:C12" si="1">2*B4</f>
         <v>157.07963267948966</v>
       </c>
-      <c r="D4" s="2">
-        <f t="shared" ref="D4:D12" si="2">4*B4</f>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46">
+        <f t="shared" ref="E4:E12" si="2">3*B4</f>
+        <v>235.61944901923448</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46">
+        <f t="shared" ref="G4:G12" si="3">4*B4</f>
         <v>314.15926535897933</v>
       </c>
-      <c r="E4" s="2">
-        <f t="shared" ref="E4:E12" si="3">8*B4</f>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46">
+        <f t="shared" ref="I4:I12" si="4">5*B4</f>
+        <v>392.69908169872417</v>
+      </c>
+      <c r="J4" s="46">
+        <f t="shared" ref="J4:J12" si="5">6*B4</f>
+        <v>471.23889803846896</v>
+      </c>
+      <c r="K4" s="46">
+        <f t="shared" ref="K4:K12" si="6">8*B4</f>
         <v>628.31853071795865</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="L4" s="39"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+    </row>
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="39"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="45">
         <v>12</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="46">
         <f t="shared" si="0"/>
         <v>113.09733552923255</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="46">
         <f t="shared" si="1"/>
         <v>226.1946710584651</v>
       </c>
-      <c r="D6" s="2">
-        <f t="shared" si="2"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46">
+        <f t="shared" ref="E6:E12" si="7">3*B6</f>
+        <v>339.29200658769764</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46">
+        <f t="shared" si="3"/>
         <v>452.38934211693021</v>
       </c>
-      <c r="E6" s="2">
-        <f t="shared" si="3"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46">
+        <f t="shared" ref="I6:I12" si="8">5*B6</f>
+        <v>565.48667764616278</v>
+      </c>
+      <c r="J6" s="46">
+        <f t="shared" ref="J6:J12" si="9">6*B6</f>
+        <v>678.58401317539528</v>
+      </c>
+      <c r="K6" s="46">
+        <f t="shared" si="6"/>
         <v>904.77868423386042</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5">
-        <f>6*B6</f>
-        <v>678.58401317539528</v>
-      </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="4">
-        <f>D6+D8</f>
+      <c r="L6" s="39"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40">
+        <f>C6+C8</f>
+        <v>628.31853071795865</v>
+      </c>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="42">
+        <f>G6+G8</f>
         <v>1256.6370614359173</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="47">
         <v>16</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="46">
         <f t="shared" si="0"/>
         <v>201.06192982974676</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="46">
         <f t="shared" si="1"/>
         <v>402.12385965949352</v>
       </c>
-      <c r="D8" s="2">
-        <f t="shared" si="2"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46">
+        <f t="shared" ref="E8:E12" si="10">3*B8</f>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="F8" s="46">
+        <f>E8+B6</f>
+        <v>716.28312501847279</v>
+      </c>
+      <c r="G8" s="46">
+        <f t="shared" si="3"/>
         <v>804.24771931898704</v>
       </c>
-      <c r="E8" s="4">
-        <f t="shared" si="3"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46">
+        <f t="shared" ref="I8:I12" si="11">5*B8</f>
+        <v>1005.3096491487338</v>
+      </c>
+      <c r="J8" s="46">
+        <f t="shared" ref="J8:J12" si="12">6*B8</f>
+        <v>1206.3715789784806</v>
+      </c>
+      <c r="K8" s="48">
+        <f t="shared" si="6"/>
         <v>1608.4954386379741</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5">
-        <f>4*B8</f>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="I8" s="21">
-        <f>H8+B6</f>
-        <v>917.34505484821955</v>
-      </c>
-      <c r="J8" s="21">
-        <f>3*B8</f>
-        <v>603.18578948924028</v>
-      </c>
-      <c r="K8" s="21">
-        <f>J8+B6</f>
-        <v>716.28312501847279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4">
-        <f>D8+D10</f>
+      <c r="L8" s="43"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="43"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42">
+        <f>G8+G10</f>
         <v>2060.8847807549046</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="47">
         <v>20</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="46">
         <f t="shared" si="0"/>
         <v>314.15926535897933</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="46">
         <f t="shared" si="1"/>
         <v>628.31853071795865</v>
       </c>
-      <c r="D10" s="2">
-        <f t="shared" si="2"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46">
+        <f t="shared" ref="E10:E12" si="13">3*B10</f>
+        <v>942.47779607693792</v>
+      </c>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46">
+        <f t="shared" si="3"/>
         <v>1256.6370614359173</v>
       </c>
-      <c r="E10" s="4">
-        <f t="shared" si="3"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46">
+        <f t="shared" ref="I10:I12" si="14">5*B10</f>
+        <v>1570.7963267948967</v>
+      </c>
+      <c r="J10" s="46">
+        <f t="shared" ref="J10:J12" si="15">6*B10</f>
+        <v>1884.9555921538758</v>
+      </c>
+      <c r="K10" s="48">
+        <f t="shared" si="6"/>
         <v>2513.2741228718346</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="21">
-        <f>C8+B6</f>
-        <v>515.22119518872603</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="4">
-        <f>D10+D12</f>
+      <c r="L10" s="43"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="44"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="42">
+        <f>G10+G12</f>
         <v>3220.1324699295383</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="45">
         <v>25</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="46">
         <f t="shared" si="0"/>
         <v>490.87385212340519</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="46">
         <f t="shared" si="1"/>
         <v>981.74770424681037</v>
       </c>
-      <c r="D12" s="2">
-        <f t="shared" si="2"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46">
+        <f t="shared" ref="E12" si="16">3*B12</f>
+        <v>1472.6215563702156</v>
+      </c>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46">
+        <f t="shared" si="3"/>
         <v>1963.4954084936207</v>
       </c>
-      <c r="E12" s="2">
-        <f t="shared" si="3"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46">
+        <f t="shared" ref="I12" si="17">5*B12</f>
+        <v>2454.3692606170262</v>
+      </c>
+      <c r="J12" s="46">
+        <f t="shared" ref="J12" si="18">6*B12</f>
+        <v>2945.2431127404311</v>
+      </c>
+      <c r="K12" s="46">
+        <f t="shared" si="6"/>
         <v>3926.9908169872415</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F15" s="21"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="50"/>
+      <c r="L15" s="44"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="49"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="51">
+        <v>1</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="53"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="51">
+        <v>2</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="53"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="51">
+        <v>3</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="53"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="51">
+        <v>4</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="53"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="37">
+        <v>5</v>
+      </c>
+      <c r="B25" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="51">
+        <v>6</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="53"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="37">
+        <v>7</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="51">
+        <v>8</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="53"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="37">
+        <v>9</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="50" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1896,421 +2775,421 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DC4736-0652-4A0E-92F2-6C6A208529DA}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="18" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
+    <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="38" t="s">
+      <c r="H2" s="23"/>
+      <c r="I2" s="34" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
+    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="39"/>
-    </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
+      <c r="I3" s="35"/>
+    </row>
+    <row r="4" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="39"/>
-    </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="25">
+      <c r="I4" s="35"/>
+    </row>
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="39"/>
-    </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+      <c r="I5" s="35"/>
+    </row>
+    <row r="6" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
         <v>5</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="39"/>
-    </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="25">
+      <c r="H6" s="23"/>
+      <c r="I6" s="35"/>
+    </row>
+    <row r="7" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="39"/>
-    </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="I7" s="35"/>
+    </row>
+    <row r="8" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="21">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="39"/>
-    </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="25">
+      <c r="I8" s="35"/>
+    </row>
+    <row r="9" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="21">
         <v>8</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="39"/>
-    </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
+      <c r="I9" s="35"/>
+    </row>
+    <row r="10" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="21">
         <v>9</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="25">
+      <c r="I10" s="35"/>
+    </row>
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="21">
         <v>10</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="27"/>
-      <c r="I11" s="39"/>
-    </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+      <c r="H11" s="23"/>
+      <c r="I11" s="35"/>
+    </row>
+    <row r="12" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="21">
         <v>11</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="25">
+      <c r="I12" s="35"/>
+    </row>
+    <row r="13" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="21">
         <v>12</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="H13" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="39"/>
-    </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+      <c r="I13" s="35"/>
+    </row>
+    <row r="14" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
         <v>13</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="H14" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="25">
+      <c r="I14" s="35"/>
+    </row>
+    <row r="15" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="21">
         <v>14</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="40"/>
+      <c r="I15" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
